--- a/output/3_continuous_bins_rules.xlsx
+++ b/output/3_continuous_bins_rules.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,12 +483,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6.50, 8.50, 10.50, 11.50</t>
+          <t>12250.00, 54005.00, 62675.00, 71675.00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-inf &lt;= Month &lt; 6.50</t>
+          <t>-inf &lt;= Credit &lt; 12250.00</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6.50, 8.50, 10.50, 11.50</t>
+          <t>12250.00, 54005.00, 62675.00, 71675.00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>6.50 &lt;= Month &lt; 8.50</t>
+          <t>12250.00 &lt;= Credit &lt; 54005.00</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -547,12 +547,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6.50, 8.50, 10.50, 11.50</t>
+          <t>12250.00, 54005.00, 62675.00, 71675.00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8.50 &lt;= Month &lt; 10.50</t>
+          <t>54005.00 &lt;= Credit &lt; 62675.00</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.50, 8.50, 10.50, 11.50</t>
+          <t>12250.00, 54005.00, 62675.00, 71675.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.50 &lt;= Month &lt; 11.50</t>
+          <t>62675.00 &lt;= Credit &lt; 71675.00</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6.50, 8.50, 10.50, 11.50</t>
+          <t>12250.00, 54005.00, 62675.00, 71675.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Month &gt;= 11.50</t>
+          <t>Credit &gt;= 71675.00</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>48655.00, 59555.00, 64550.00, 71675.00</t>
+          <t>26.50, 30.50, 39.50, 58.50</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-inf &lt;= Credit &lt; 48655.00</t>
+          <t>-inf &lt;= Age &lt; 26.50</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -675,12 +675,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>48655.00, 59555.00, 64550.00, 71675.00</t>
+          <t>26.50, 30.50, 39.50, 58.50</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48655.00 &lt;= Credit &lt; 59555.00</t>
+          <t>26.50 &lt;= Age &lt; 30.50</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48655.00, 59555.00, 64550.00, 71675.00</t>
+          <t>26.50, 30.50, 39.50, 58.50</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>59555.00 &lt;= Credit &lt; 64550.00</t>
+          <t>30.50 &lt;= Age &lt; 39.50</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -739,12 +739,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>48655.00, 59555.00, 64550.00, 71675.00</t>
+          <t>26.50, 30.50, 39.50, 58.50</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>64550.00 &lt;= Credit &lt; 71675.00</t>
+          <t>39.50 &lt;= Age &lt; 58.50</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -771,12 +771,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>48655.00, 59555.00, 64550.00, 71675.00</t>
+          <t>26.50, 30.50, 39.50, 58.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Credit &gt;= 71675.00</t>
+          <t>Age &gt;= 58.50</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>AnnualIncome</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>26.50, 30.50, 39.50, 59.50</t>
+          <t>42.00, 2530.00, 62330.00, 130657.00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-inf &lt;= Age &lt; 26.50</t>
+          <t>-inf &lt;= AnnualIncome &lt; 42.00</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>AnnualIncome</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26.50, 30.50, 39.50, 59.50</t>
+          <t>42.00, 2530.00, 62330.00, 130657.00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>26.50 &lt;= Age &lt; 30.50</t>
+          <t>42.00 &lt;= AnnualIncome &lt; 2530.00</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>AnnualIncome</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26.50, 30.50, 39.50, 59.50</t>
+          <t>42.00, 2530.00, 62330.00, 130657.00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30.50 &lt;= Age &lt; 39.50</t>
+          <t>2530.00 &lt;= AnnualIncome &lt; 62330.00</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>AnnualIncome</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -899,12 +899,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>26.50, 30.50, 39.50, 59.50</t>
+          <t>42.00, 2530.00, 62330.00, 130657.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>39.50 &lt;= Age &lt; 59.50</t>
+          <t>62330.00 &lt;= AnnualIncome &lt; 130657.00</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>AnnualIncome</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26.50, 30.50, 39.50, 59.50</t>
+          <t>42.00, 2530.00, 62330.00, 130657.00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Age &gt;= 59.50</t>
+          <t>AnnualIncome &gt;= 130657.00</t>
         </is>
       </c>
     </row>
@@ -948,27 +948,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AnnualIncome</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bin_0</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24364.50, 24523.50, 62231.00, 130650.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-inf &lt;= AnnualIncome &lt; 24364.50</t>
+          <t>ServiceType == C</t>
         </is>
       </c>
     </row>
@@ -980,27 +980,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AnnualIncome</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bin_1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24364.50, 24523.50, 62231.00, 130650.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>24364.50 &lt;= AnnualIncome &lt; 24523.50</t>
+          <t>ServiceType == E</t>
         </is>
       </c>
     </row>
@@ -1012,27 +1012,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AnnualIncome</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bin_2</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24364.50, 24523.50, 62231.00, 130650.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>24523.50 &lt;= AnnualIncome &lt; 62231.00</t>
+          <t>ServiceType == H</t>
         </is>
       </c>
     </row>
@@ -1044,27 +1044,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AnnualIncome</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bin_3</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>24364.50, 24523.50, 62231.00, 130650.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>62231.00 &lt;= AnnualIncome &lt; 130650.50</t>
+          <t>ServiceType == I</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AnnualIncome</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bin_4</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>24364.50, 24523.50, 62231.00, 130650.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AnnualIncome &gt;= 130650.50</t>
+          <t>ServiceType == M</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Year == 2010</t>
+          <t>ServiceType == N</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Year == 2011</t>
+          <t>ServiceType == S</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Year == 2012</t>
+          <t>Government == Y</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ServiceType == C</t>
+          <t>Market == Internet</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ServiceType == E</t>
+          <t>Market == Midwest</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>MountainPlains</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ServiceType == H</t>
+          <t>Market == MountainPlains</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ServiceType == I</t>
+          <t>Market == Northeast</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ServiceType == M</t>
+          <t>Market == Southeast</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ServiceType == N</t>
+          <t>Market == Southwest</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Western</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ServiceType == S</t>
+          <t>Market == Western</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>NewCustomer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Government == Y</t>
+          <t>NewCustomer == Y</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>PaymentMethod</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Market == Internet</t>
+          <t>PaymentMethod == Direct</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>PaymentMethod</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Gov</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Market == Midwest</t>
+          <t>PaymentMethod == Gov</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>PaymentMethod</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MountainPlains</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Market == MountainPlains</t>
+          <t>PaymentMethod == Other</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Market == Northeast</t>
+          <t>Gender == M</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>Dependents</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Market == Southeast</t>
+          <t>Dependents == No</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>Dependents</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Southwest</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Market == Southwest</t>
+          <t>Dependents == Yes</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>MaritalStatus</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Western</t>
+          <t>Married</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Market == Western</t>
+          <t>MaritalStatus == Married</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NewCustomer</t>
+          <t>MaritalStatus</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Separ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NewCustomer == Y</t>
+          <t>MaritalStatus == Separ</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PaymentMethod</t>
+          <t>MaritalStatus</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PaymentMethod == Direct</t>
+          <t>MaritalStatus == Single</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PaymentMethod</t>
+          <t>Classification1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Gov</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PaymentMethod == Gov</t>
+          <t>Classification1 == 1</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PaymentMethod</t>
+          <t>Classification1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PaymentMethod == Other</t>
+          <t>Classification1 == 2</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Classification1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gender == M</t>
+          <t>Classification1 == 3</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dependents</t>
+          <t>Classification1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dependents == No</t>
+          <t>Classification1 == 4</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dependents</t>
+          <t>Classification2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dependents == Yes</t>
+          <t>Classification2 == 1</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MaritalStatus</t>
+          <t>Classification2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Married</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MaritalStatus == Married</t>
+          <t>Classification2 == 2</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MaritalStatus</t>
+          <t>Classification2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Separ</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MaritalStatus == Separ</t>
+          <t>Classification2 == 3</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MaritalStatus</t>
+          <t>Classification2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1992,263 +1992,263 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MaritalStatus == Single</t>
+          <t>Classification2 == 4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>High Group</t>
+          <t>Low Group</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Classification1</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Categorical</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Bin_0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2835.00, 40685.00, 50715.00, 58840.00</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Classification1 == 1</t>
+          <t>-inf &lt;= Credit &lt; 2835.00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>High Group</t>
+          <t>Low Group</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Classification1</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Categorical</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Bin_1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2835.00, 40685.00, 50715.00, 58840.00</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Classification1 == 2</t>
+          <t>2835.00 &lt;= Credit &lt; 40685.00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>High Group</t>
+          <t>Low Group</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Classification1</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Categorical</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bin_2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2835.00, 40685.00, 50715.00, 58840.00</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Classification1 == 3</t>
+          <t>40685.00 &lt;= Credit &lt; 50715.00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>High Group</t>
+          <t>Low Group</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Classification1</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Categorical</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Bin_3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2835.00, 40685.00, 50715.00, 58840.00</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Classification1 == 4</t>
+          <t>50715.00 &lt;= Credit &lt; 58840.00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>High Group</t>
+          <t>Low Group</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Classification2</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Categorical</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Bin_4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2835.00, 40685.00, 50715.00, 58840.00</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Classification2 == 1</t>
+          <t>Credit &gt;= 58840.00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>High Group</t>
+          <t>Low Group</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Classification2</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Categorical</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Bin_0</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>21.50, 29.50, 52.50, 65.50</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Classification2 == 2</t>
+          <t>-inf &lt;= Age &lt; 21.50</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>High Group</t>
+          <t>Low Group</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Classification2</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Categorical</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bin_1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>21.50, 29.50, 52.50, 65.50</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Classification2 == 3</t>
+          <t>21.50 &lt;= Age &lt; 29.50</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>High Group</t>
+          <t>Low Group</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Classification2</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Categorical</t>
+          <t>Continuous</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Bin_2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>21.50, 29.50, 52.50, 65.50</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Classification2 == 4</t>
+          <t>29.50 &lt;= Age &lt; 52.50</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2270,17 +2270,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Bin_0</t>
+          <t>Bin_3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.50, 2.50, 9.50, 11.50</t>
+          <t>21.50, 29.50, 52.50, 65.50</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-inf &lt;= Month &lt; 1.50</t>
+          <t>52.50 &lt;= Age &lt; 65.50</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2302,17 +2302,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Bin_1</t>
+          <t>Bin_4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.50, 2.50, 9.50, 11.50</t>
+          <t>21.50, 29.50, 52.50, 65.50</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.50 &lt;= Month &lt; 2.50</t>
+          <t>Age &gt;= 65.50</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AnnualIncome</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Bin_2</t>
+          <t>Bin_0</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.50, 2.50, 9.50, 11.50</t>
+          <t>123.00, 19323.00, 26230.00, 70077.50</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2.50 &lt;= Month &lt; 9.50</t>
+          <t>-inf &lt;= AnnualIncome &lt; 123.00</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AnnualIncome</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2366,17 +2366,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Bin_3</t>
+          <t>Bin_1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.50, 2.50, 9.50, 11.50</t>
+          <t>123.00, 19323.00, 26230.00, 70077.50</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>9.50 &lt;= Month &lt; 11.50</t>
+          <t>123.00 &lt;= AnnualIncome &lt; 19323.00</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AnnualIncome</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2398,17 +2398,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Bin_4</t>
+          <t>Bin_2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.50, 2.50, 9.50, 11.50</t>
+          <t>123.00, 19323.00, 26230.00, 70077.50</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Month &gt;= 11.50</t>
+          <t>19323.00 &lt;= AnnualIncome &lt; 26230.00</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>AnnualIncome</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Bin_0</t>
+          <t>Bin_3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>10580.00, 40335.00, 49005.00, 50665.00</t>
+          <t>123.00, 19323.00, 26230.00, 70077.50</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-inf &lt;= Credit &lt; 10580.00</t>
+          <t>26230.00 &lt;= AnnualIncome &lt; 70077.50</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>AnnualIncome</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Bin_1</t>
+          <t>Bin_4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>10580.00, 40335.00, 49005.00, 50665.00</t>
+          <t>123.00, 19323.00, 26230.00, 70077.50</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>10580.00 &lt;= Credit &lt; 40335.00</t>
+          <t>AnnualIncome &gt;= 70077.50</t>
         </is>
       </c>
     </row>
@@ -2484,27 +2484,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Bin_2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>10580.00, 40335.00, 49005.00, 50665.00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>40335.00 &lt;= Credit &lt; 49005.00</t>
+          <t>ServiceType == C</t>
         </is>
       </c>
     </row>
@@ -2516,27 +2516,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Bin_3</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>10580.00, 40335.00, 49005.00, 50665.00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>49005.00 &lt;= Credit &lt; 50665.00</t>
+          <t>ServiceType == E</t>
         </is>
       </c>
     </row>
@@ -2548,27 +2548,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Bin_4</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>10580.00, 40335.00, 49005.00, 50665.00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Credit &gt;= 50665.00</t>
+          <t>ServiceType == H</t>
         </is>
       </c>
     </row>
@@ -2580,27 +2580,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Bin_0</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>21.50, 29.50, 42.50, 47.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-inf &lt;= Age &lt; 21.50</t>
+          <t>ServiceType == I</t>
         </is>
       </c>
     </row>
@@ -2612,27 +2612,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Bin_1</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>21.50, 29.50, 42.50, 47.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>21.50 &lt;= Age &lt; 29.50</t>
+          <t>ServiceType == M</t>
         </is>
       </c>
     </row>
@@ -2644,27 +2644,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Bin_2</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>21.50, 29.50, 42.50, 47.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>29.50 &lt;= Age &lt; 42.50</t>
+          <t>ServiceType == N</t>
         </is>
       </c>
     </row>
@@ -2676,27 +2676,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>ServiceType</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Bin_3</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>21.50, 29.50, 42.50, 47.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>42.50 &lt;= Age &lt; 47.50</t>
+          <t>ServiceType == S</t>
         </is>
       </c>
     </row>
@@ -2708,27 +2708,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Bin_4</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>21.50, 29.50, 42.50, 47.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Age &gt;= 47.50</t>
+          <t>Government == Y</t>
         </is>
       </c>
     </row>
@@ -2740,27 +2740,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AnnualIncome</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Bin_0</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0.50, 518.50, 28814.50, 28966.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-inf &lt;= AnnualIncome &lt; 0.50</t>
+          <t>Market == Midwest</t>
         </is>
       </c>
     </row>
@@ -2772,27 +2772,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AnnualIncome</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Bin_1</t>
+          <t>MountainPlains</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0.50, 518.50, 28814.50, 28966.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.50 &lt;= AnnualIncome &lt; 518.50</t>
+          <t>Market == MountainPlains</t>
         </is>
       </c>
     </row>
@@ -2804,27 +2804,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AnnualIncome</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Bin_2</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0.50, 518.50, 28814.50, 28966.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>518.50 &lt;= AnnualIncome &lt; 28814.50</t>
+          <t>Market == Northeast</t>
         </is>
       </c>
     </row>
@@ -2836,27 +2836,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AnnualIncome</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Bin_3</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0.50, 518.50, 28814.50, 28966.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>28814.50 &lt;= AnnualIncome &lt; 28966.50</t>
+          <t>Market == Southeast</t>
         </is>
       </c>
     </row>
@@ -2868,27 +2868,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AnnualIncome</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Categorical</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Bin_4</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0.50, 518.50, 28814.50, 28966.50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AnnualIncome &gt;= 28966.50</t>
+          <t>Market == Southwest</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>Western</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Year == 2010</t>
+          <t>Market == Western</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>NewCustomer</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Year == 2011</t>
+          <t>NewCustomer == Y</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>PaymentMethod</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Year == 2012</t>
+          <t>PaymentMethod == Direct</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>PaymentMethod</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Gov</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ServiceType == C</t>
+          <t>PaymentMethod == Gov</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>PaymentMethod</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ServiceType == E</t>
+          <t>PaymentMethod == Other</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ServiceType == H</t>
+          <t>Gender == M</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>Dependents</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ServiceType == I</t>
+          <t>Dependents == No</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>Dependents</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ServiceType == M</t>
+          <t>Dependents == Yes</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>MaritalStatus</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Married</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ServiceType == N</t>
+          <t>MaritalStatus == Married</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ServiceType</t>
+          <t>MaritalStatus</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Separ</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ServiceType == S</t>
+          <t>MaritalStatus == Separ</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>MaritalStatus</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Government == Y</t>
+          <t>MaritalStatus == Single</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>Classification1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Market == Midwest</t>
+          <t>Classification1 == 1</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>Classification1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>MountainPlains</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Market == MountainPlains</t>
+          <t>Classification1 == 2</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>Classification1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Market == Northeast</t>
+          <t>Classification1 == 3</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>Classification1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Market == Southeast</t>
+          <t>Classification1 == 4</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>Classification2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Southwest</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Market == Southwest</t>
+          <t>Classification2 == 1</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>Classification2</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Western</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Market == Western</t>
+          <t>Classification2 == 2</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NewCustomer</t>
+          <t>Classification2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>NewCustomer == Y</t>
+          <t>Classification2 == 3</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PaymentMethod</t>
+          <t>Classification2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3495,518 +3495,6 @@
         </is>
       </c>
       <c r="F96" t="inlineStr">
-        <is>
-          <t>PaymentMethod == Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>PaymentMethod</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Gov</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>PaymentMethod == Gov</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>PaymentMethod</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>PaymentMethod == Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Gender</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Gender == M</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Dependents</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Dependents == No</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Dependents</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Dependents == Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>MaritalStatus</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Married</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>MaritalStatus == Married</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>MaritalStatus</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Separ</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>MaritalStatus == Separ</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>MaritalStatus</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>MaritalStatus == Single</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Classification1</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Classification1 == 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Classification1</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Classification1 == 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Classification1</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Classification1 == 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Classification1</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Classification1 == 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Classification2</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Classification2 == 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Classification2</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Classification2 == 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Classification2</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Classification2 == 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Classification2</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Categorical</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
         <is>
           <t>Classification2 == 4</t>
         </is>
